--- a/docs/tech/ezEKP_시스템_사이징_사용자수별.xlsx
+++ b/docs/tech/ezEKP_시스템_사이징_사용자수별.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kaoni\jmocha\sizing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\kaoni\jmocha\ezFlow4Java\docs\tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
   <si>
     <t>Software</t>
   </si>
@@ -234,10 +234,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>그룹웨어(문서) 용량 / Mbytes</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">1인당 메일 할당량 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -246,43 +242,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>메일 사용(용량) 비율 (60%)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>메일 사용용량 비율(Batch로 주기적 삭제기준)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>그룹웨어(메일) 용량 / Mbytes</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>시스템 사용용량 (Tbytes)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>그룹웨어 문서 사용량 (Tbytes)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>그룹웨어 문서 용량 (5년사용기준)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>그룹웨어 메일 사용량 (Tbytes)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>그룹웨어 메일 용량</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Storage 여유율</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Disk 사용률 85%이하 유지 권장</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -292,11 +252,6 @@
   <si>
     <t>ezEKP 시스템 서버 표준사이징</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>메일 큐(1인당 100MB)및 LOG 사용량(1인당 300MB) / 게시,공지 첨부파일 등(1인당 500MB) / 
-대용량 파일저장 용량(1인당 100MB)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>garbd(이중화 시)</t>
@@ -523,6 +478,50 @@
       </rPr>
       <t>(이중화)</t>
     </r>
+  </si>
+  <si>
+    <t>게시,공지 첨부파일 등
+(1인당 1년 사용량)</t>
+  </si>
+  <si>
+    <t>그룹웨어 용량 / Mbytes</t>
+  </si>
+  <si>
+    <t>메일 용량 / Mbytes</t>
+  </si>
+  <si>
+    <t>메일 용량</t>
+  </si>
+  <si>
+    <t>메일 사용(용량) 비율</t>
+  </si>
+  <si>
+    <t>메일 사용용량 비율</t>
+  </si>
+  <si>
+    <t>대용량 첨부파일 (1인당 사용량)</t>
+  </si>
+  <si>
+    <t>대용량 첨부파일 14일간 보존 기준</t>
+  </si>
+  <si>
+    <t>그룹웨어 용량 (Tbytes)</t>
+  </si>
+  <si>
+    <t>메일 용량 (Tbytes)</t>
+  </si>
+  <si>
+    <t>로컬 시스템 용량 
+(Tbytes)</t>
+  </si>
+  <si>
+    <t>Disk 사용률 90%이하 유지 권장</t>
+  </si>
+  <si>
+    <t>메일 큐(1인당 100MB)및 LOG 사용량(1인당 300MB) (이중화시 서버간 공유되지 않음)</t>
+  </si>
+  <si>
+    <t>그룹웨어 용량</t>
   </si>
 </sst>
 </file>
@@ -902,7 +901,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -976,6 +975,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1355,7 +1366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1368,49 +1379,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="55" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
+      <c r="A1" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
+      <c r="A2" s="59"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
     </row>
     <row r="3" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="56" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1426,14 +1437,14 @@
         <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="74.25" customHeight="1" thickBot="1">
-      <c r="A6" s="48"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="8" t="s">
         <v>8</v>
       </c>
@@ -1441,22 +1452,22 @@
         <v>6</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="46.5" customHeight="1">
-      <c r="A7" s="49"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="19" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
@@ -1476,7 +1487,7 @@
     </row>
     <row r="8" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="9" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="56" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1492,35 +1503,35 @@
         <v>2</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A10" s="48"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="20" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="54" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
@@ -1528,19 +1539,19 @@
         <v>6</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>5</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="51"/>
+        <v>60</v>
+      </c>
+      <c r="G11" s="55"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="13" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="56" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1556,35 +1567,35 @@
         <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A14" s="48"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G14" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="54" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A15" s="49"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
@@ -1592,19 +1603,19 @@
         <v>7</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>5</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="51"/>
+        <v>62</v>
+      </c>
+      <c r="G15" s="55"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="17" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A17" s="47" t="s">
+      <c r="A17" s="51" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1620,35 +1631,35 @@
         <v>2</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A18" s="48"/>
+      <c r="A18" s="52"/>
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E18" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" s="50" t="s">
+      <c r="G18" s="54" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A19" s="49"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="3" t="s">
         <v>10</v>
       </c>
@@ -1656,15 +1667,15 @@
         <v>7</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="51"/>
+        <v>63</v>
+      </c>
+      <c r="G19" s="55"/>
     </row>
     <row r="21" spans="1:7">
       <c r="B21" s="11" t="s">
@@ -1679,10 +1690,10 @@
       <c r="E21" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="45" t="s">
+      <c r="F21" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G21" s="46"/>
+      <c r="G21" s="50"/>
     </row>
     <row r="22" spans="1:7">
       <c r="B22" s="12">
@@ -1692,13 +1703,13 @@
         <v>36</v>
       </c>
       <c r="D22" s="13">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="E22" s="13"/>
-      <c r="F22" s="25" t="s">
+      <c r="F22" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="26"/>
+      <c r="G22" s="30"/>
     </row>
     <row r="23" spans="1:7" ht="25.5">
       <c r="B23" s="12">
@@ -1711,10 +1722,10 @@
         <v>1</v>
       </c>
       <c r="E23" s="15"/>
-      <c r="F23" s="25" t="s">
+      <c r="F23" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="G23" s="26"/>
+      <c r="G23" s="30"/>
     </row>
     <row r="24" spans="1:7" ht="25.5">
       <c r="B24" s="12">
@@ -1727,10 +1738,10 @@
         <v>22</v>
       </c>
       <c r="E24" s="15"/>
-      <c r="F24" s="25" t="s">
+      <c r="F24" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="G24" s="26"/>
+      <c r="G24" s="30"/>
     </row>
     <row r="25" spans="1:7">
       <c r="B25" s="12">
@@ -1743,10 +1754,10 @@
         <v>12</v>
       </c>
       <c r="E25" s="15"/>
-      <c r="F25" s="25" t="s">
+      <c r="F25" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="26"/>
+      <c r="G25" s="30"/>
     </row>
     <row r="26" spans="1:7" ht="25.5">
       <c r="B26" s="12">
@@ -1759,10 +1770,10 @@
         <v>5</v>
       </c>
       <c r="E26" s="15"/>
-      <c r="F26" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="26"/>
+      <c r="F26" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26" s="30"/>
     </row>
     <row r="27" spans="1:7" ht="25.5">
       <c r="B27" s="12">
@@ -1775,151 +1786,181 @@
         <v>0.3</v>
       </c>
       <c r="E27" s="16"/>
-      <c r="F27" s="25" t="s">
+      <c r="F27" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="G27" s="26"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="B28" s="39" t="s">
+      <c r="G27" s="30"/>
+    </row>
+    <row r="28" spans="1:7" ht="51">
+      <c r="B28" s="12">
+        <v>7</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="14">
+        <v>100</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="26"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="B29" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="44"/>
+      <c r="D29" s="45">
+        <f>D22*D23*D24*D25*D26*D27 + D22*D26*D28</f>
+        <v>896000</v>
+      </c>
+      <c r="E29" s="46"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="48"/>
+    </row>
+    <row r="30" spans="1:7" ht="25.5">
+      <c r="B30" s="12">
+        <v>1</v>
+      </c>
+      <c r="C30" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="41">
-        <f>D22*D23*D24*D25*D26*D27</f>
-        <v>2772000</v>
-      </c>
-      <c r="E28" s="42"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="44"/>
-    </row>
-    <row r="29" spans="1:7" ht="25.5">
-      <c r="B29" s="12">
+      <c r="D30" s="14">
+        <v>1000</v>
+      </c>
+      <c r="E30" s="15"/>
+      <c r="F30" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="G30" s="30"/>
+    </row>
+    <row r="31" spans="1:7" ht="38.25">
+      <c r="B31" s="12">
+        <v>2</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="17">
         <v>1</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1000</v>
-      </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="G29" s="26"/>
-    </row>
-    <row r="30" spans="1:7" ht="38.25">
-      <c r="B30" s="12">
-        <v>2</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="17">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="G30" s="26"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="B31" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="40"/>
-      <c r="D31" s="41">
-        <f>D22*D29*1.2*D30</f>
-        <v>8400000</v>
-      </c>
-      <c r="E31" s="42"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="44"/>
-    </row>
-    <row r="32" spans="1:7" ht="38.25">
+      <c r="E31" s="15"/>
+      <c r="F31" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="G31" s="30"/>
+    </row>
+    <row r="32" spans="1:7" ht="51">
       <c r="B32" s="12">
-        <v>1</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="33">
-        <f>0.0005*D22 + 0.0001*D22 + 0.0004*D22</f>
-        <v>7</v>
-      </c>
-      <c r="E32" s="34"/>
+        <v>3</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="14">
+        <v>100</v>
+      </c>
+      <c r="E32" s="28"/>
       <c r="F32" s="25" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="G32" s="26"/>
     </row>
-    <row r="33" spans="2:7" ht="38.25">
-      <c r="B33" s="12">
-        <v>2</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D33" s="35">
-        <f>D28/1000000</f>
-        <v>2.7719999999999998</v>
-      </c>
-      <c r="E33" s="36"/>
-      <c r="F33" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="G33" s="26"/>
+    <row r="33" spans="2:7">
+      <c r="B33" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="44"/>
+      <c r="D33" s="45">
+        <f>D22*D30*1.2*D31 + D22*D32</f>
+        <v>1300000</v>
+      </c>
+      <c r="E33" s="46"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="48"/>
     </row>
     <row r="34" spans="2:7" ht="38.25">
       <c r="B34" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="D34" s="37">
-        <f>D31/1000000</f>
-        <v>8.4</v>
+        <f>0.0001*D22 + 0.0003*D22</f>
+        <v>0.4</v>
       </c>
       <c r="E34" s="38"/>
-      <c r="F34" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="G34" s="26"/>
+      <c r="F34" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="G34" s="30"/>
     </row>
     <row r="35" spans="2:7" ht="25.5">
       <c r="B35" s="12">
+        <v>2</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" s="39">
+        <f>D29/1000000</f>
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="E35" s="40"/>
+      <c r="F35" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="G35" s="30"/>
+    </row>
+    <row r="36" spans="2:7" ht="25.5">
+      <c r="B36" s="12">
+        <v>3</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="41">
+        <f>D33/1000000</f>
+        <v>1.3</v>
+      </c>
+      <c r="E36" s="42"/>
+      <c r="F36" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="G36" s="30"/>
+    </row>
+    <row r="37" spans="2:7" ht="25.5">
+      <c r="B37" s="12">
         <v>4</v>
       </c>
-      <c r="C35" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35" s="24">
+      <c r="C37" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37" s="24">
         <v>10</v>
       </c>
-      <c r="E35" s="18">
-        <f>SUM(D32:E34)/(1 - D35/100)</f>
-        <v>20.191111111111113</v>
-      </c>
-      <c r="F35" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="G35" s="26"/>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="28"/>
-      <c r="D36" s="29">
-        <f>E35</f>
-        <v>20.191111111111113</v>
-      </c>
-      <c r="E36" s="30"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="32"/>
+      <c r="E37" s="18">
+        <f>SUM(D34:E36)/(1 - D37/100)</f>
+        <v>2.8844444444444446</v>
+      </c>
+      <c r="F37" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="G37" s="30"/>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="32"/>
+      <c r="D38" s="33">
+        <f>E37</f>
+        <v>2.8844444444444446</v>
+      </c>
+      <c r="E38" s="34"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="35">
@@ -1940,24 +1981,24 @@
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:G31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="D35:E35"/>
     <mergeCell ref="F35:G35"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="F36:G36"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/tech/ezEKP_시스템_사이징_사용자수별.xlsx
+++ b/docs/tech/ezEKP_시스템_사이징_사용자수별.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="88">
   <si>
     <t>Software</t>
   </si>
@@ -522,6 +522,27 @@
   </si>
   <si>
     <t>그룹웨어 용량</t>
+  </si>
+  <si>
+    <t>로컬 리스템 용량</t>
+  </si>
+  <si>
+    <t>그룹웨어 용량 + 
+대용량 첨부파일</t>
+  </si>
+  <si>
+    <t>메일용량</t>
+  </si>
+  <si>
+    <t>이중화시 서버마다 다른 Data가 저장되는 용량</t>
+  </si>
+  <si>
+    <t>이중화시 서버간 동일 Data가 저장되는 DB Data 용량 
+(MariaDB의 경우엔 복제 방식이므로 서버당 용량이 필요하며  Oracle의 경우엔 Shared Disk 방식이므로 단일 용량만 필요)</t>
+  </si>
+  <si>
+    <t>이중화시 서버간 동일 Data가 저장되는 File Data 용량
+(GlusterFS의 경우엔 복제 방식이므로 서버당 용량이 필요하며 NAS 혹은 네트워크 파일 시스템을 사용할 경우엔 단일 용량만 필요)</t>
   </si>
 </sst>
 </file>
@@ -901,7 +922,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -989,11 +1010,65 @@
     <xf numFmtId="3" fontId="12" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1031,59 +1106,11 @@
     <xf numFmtId="167" fontId="11" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1366,11 +1393,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="35.5703125" customWidth="1"/>
+    <col min="2" max="2" width="37.85546875" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" customWidth="1"/>
     <col min="4" max="4" width="8.85546875" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
@@ -1379,49 +1406,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="59"/>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="33" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1444,7 +1471,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="74.25" customHeight="1" thickBot="1">
-      <c r="A6" s="52"/>
+      <c r="A6" s="34"/>
       <c r="B6" s="8" t="s">
         <v>8</v>
       </c>
@@ -1465,7 +1492,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="46.5" customHeight="1">
-      <c r="A7" s="53"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="19" t="s">
         <v>51</v>
       </c>
@@ -1487,7 +1514,7 @@
     </row>
     <row r="8" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="9" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A9" s="56" t="s">
+      <c r="A9" s="33" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1510,7 +1537,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A10" s="52"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="20" t="s">
         <v>52</v>
       </c>
@@ -1526,12 +1553,12 @@
       <c r="F10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="54" t="s">
+      <c r="G10" s="36" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A11" s="53"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
@@ -1547,11 +1574,11 @@
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="55"/>
+      <c r="G11" s="37"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="13" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1574,7 +1601,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A14" s="52"/>
+      <c r="A14" s="34"/>
       <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
@@ -1590,12 +1617,12 @@
       <c r="F14" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G14" s="54" t="s">
+      <c r="G14" s="36" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A15" s="53"/>
+      <c r="A15" s="35"/>
       <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
@@ -1611,11 +1638,11 @@
       <c r="F15" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="55"/>
+      <c r="G15" s="37"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="17" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="38" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1638,7 +1665,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A18" s="52"/>
+      <c r="A18" s="34"/>
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
@@ -1654,12 +1681,12 @@
       <c r="F18" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="G18" s="54" t="s">
+      <c r="G18" s="36" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A19" s="53"/>
+      <c r="A19" s="35"/>
       <c r="B19" s="3" t="s">
         <v>10</v>
       </c>
@@ -1675,7 +1702,7 @@
       <c r="F19" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="55"/>
+      <c r="G19" s="37"/>
     </row>
     <row r="21" spans="1:7">
       <c r="B21" s="11" t="s">
@@ -1690,10 +1717,10 @@
       <c r="E21" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="49" t="s">
+      <c r="F21" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="G21" s="50"/>
+      <c r="G21" s="40"/>
     </row>
     <row r="22" spans="1:7">
       <c r="B22" s="12">
@@ -1706,10 +1733,10 @@
         <v>1000</v>
       </c>
       <c r="E22" s="13"/>
-      <c r="F22" s="29" t="s">
+      <c r="F22" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="30"/>
+      <c r="G22" s="42"/>
     </row>
     <row r="23" spans="1:7" ht="25.5">
       <c r="B23" s="12">
@@ -1722,10 +1749,10 @@
         <v>1</v>
       </c>
       <c r="E23" s="15"/>
-      <c r="F23" s="29" t="s">
+      <c r="F23" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="G23" s="30"/>
+      <c r="G23" s="42"/>
     </row>
     <row r="24" spans="1:7" ht="25.5">
       <c r="B24" s="12">
@@ -1738,10 +1765,10 @@
         <v>22</v>
       </c>
       <c r="E24" s="15"/>
-      <c r="F24" s="29" t="s">
+      <c r="F24" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="G24" s="30"/>
+      <c r="G24" s="42"/>
     </row>
     <row r="25" spans="1:7">
       <c r="B25" s="12">
@@ -1754,10 +1781,10 @@
         <v>12</v>
       </c>
       <c r="E25" s="15"/>
-      <c r="F25" s="29" t="s">
+      <c r="F25" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="30"/>
+      <c r="G25" s="42"/>
     </row>
     <row r="26" spans="1:7" ht="25.5">
       <c r="B26" s="12">
@@ -1770,10 +1797,10 @@
         <v>5</v>
       </c>
       <c r="E26" s="15"/>
-      <c r="F26" s="29" t="s">
+      <c r="F26" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="G26" s="30"/>
+      <c r="G26" s="42"/>
     </row>
     <row r="27" spans="1:7" ht="25.5">
       <c r="B27" s="12">
@@ -1786,10 +1813,10 @@
         <v>0.3</v>
       </c>
       <c r="E27" s="16"/>
-      <c r="F27" s="29" t="s">
+      <c r="F27" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="G27" s="30"/>
+      <c r="G27" s="42"/>
     </row>
     <row r="28" spans="1:7" ht="51">
       <c r="B28" s="12">
@@ -1829,10 +1856,10 @@
         <v>1000</v>
       </c>
       <c r="E30" s="15"/>
-      <c r="F30" s="29" t="s">
+      <c r="F30" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="30"/>
+      <c r="G30" s="42"/>
     </row>
     <row r="31" spans="1:7" ht="38.25">
       <c r="B31" s="12">
@@ -1845,10 +1872,10 @@
         <v>1</v>
       </c>
       <c r="E31" s="15"/>
-      <c r="F31" s="29" t="s">
+      <c r="F31" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="G31" s="30"/>
+      <c r="G31" s="42"/>
     </row>
     <row r="32" spans="1:7" ht="51">
       <c r="B32" s="12">
@@ -1886,15 +1913,15 @@
       <c r="C34" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D34" s="37">
+      <c r="D34" s="55">
         <f>0.0001*D22 + 0.0003*D22</f>
         <v>0.4</v>
       </c>
-      <c r="E34" s="38"/>
-      <c r="F34" s="29" t="s">
+      <c r="E34" s="56"/>
+      <c r="F34" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="G34" s="30"/>
+      <c r="G34" s="42"/>
     </row>
     <row r="35" spans="2:7" ht="25.5">
       <c r="B35" s="12">
@@ -1903,15 +1930,15 @@
       <c r="C35" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="57">
         <f>D29/1000000</f>
         <v>0.89600000000000002</v>
       </c>
-      <c r="E35" s="40"/>
-      <c r="F35" s="29" t="s">
+      <c r="E35" s="58"/>
+      <c r="F35" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="G35" s="30"/>
+      <c r="G35" s="42"/>
     </row>
     <row r="36" spans="2:7" ht="25.5">
       <c r="B36" s="12">
@@ -1920,15 +1947,15 @@
       <c r="C36" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="41">
+      <c r="D36" s="59">
         <f>D33/1000000</f>
         <v>1.3</v>
       </c>
-      <c r="E36" s="42"/>
-      <c r="F36" s="29" t="s">
+      <c r="E36" s="60"/>
+      <c r="F36" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="G36" s="30"/>
+      <c r="G36" s="42"/>
     </row>
     <row r="37" spans="2:7" ht="25.5">
       <c r="B37" s="12">
@@ -1944,51 +1971,50 @@
         <f>SUM(D34:E36)/(1 - D37/100)</f>
         <v>2.8844444444444446</v>
       </c>
-      <c r="F37" s="29" t="s">
+      <c r="F37" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="G37" s="30"/>
+      <c r="G37" s="42"/>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="31" t="s">
+      <c r="B38" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="32"/>
-      <c r="D38" s="33">
+      <c r="C38" s="50"/>
+      <c r="D38" s="51">
         <f>E37</f>
         <v>2.8844444444444446</v>
       </c>
-      <c r="E38" s="34"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="36"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="54"/>
+    </row>
+    <row r="40" spans="2:7" ht="30">
+      <c r="B40" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" s="61" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="90">
+      <c r="B41" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="61" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" ht="90">
+      <c r="B42" s="62" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="61" t="s">
+        <v>84</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="D38:E38"/>
@@ -1999,6 +2025,31 @@
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="G10:G11"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/tech/ezEKP_시스템_사이징_사용자수별.xlsx
+++ b/docs/tech/ezEKP_시스템_사이징_사용자수별.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\kaoni\jmocha\ezFlow4Java\docs\tech\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Projects\kaoni\jmocha\ezFlow4Java\docs\tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="83">
   <si>
     <t>Software</t>
   </si>
@@ -43,10 +43,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>32GB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1(단중화)
 2(이중화)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -55,23 +51,6 @@
     <t>2(단중화)
 3(이중화)</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tomcat, GlusterFS(이중화 시)
-JMocha Gateway Server, JMocha Mail Server, MariaDB</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tomcat, GlusterFS(이중화 시)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>JMocha Gateway Server, JMocha Mail Server, MariaDB</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>JMocha Gateway Server, JMocha Mail Server, MariaDB</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -130,19 +109,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>32GB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1 x 1core</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>4GB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> - 100GB</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -158,10 +129,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>• garbd는 MariaDB Cluster의 노드수를 홀수로 만들기 위해 사용하는 가상노드임</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">• HDD는 SAS 10,000rpm 이상 필요
 </t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -258,14 +225,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Tomcat, GlusterFS(이중화 시), garbd(이중화 시)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>64GB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>서버당 Storage</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -275,159 +234,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1 x 8core
-2.4GHz</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 x 16core
-2.4GHz</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> - 사용자당 메일박스용량 x 1.2 x 사용자수
-   예) 사용자당 1GB일 경우 1GB x 1.2 x 1,000 = 1.2TB
- - 사용자당 대용량 첨부 파일저장용량 x 사용자수
-   예) 보관기간 14일 동안 사용자당 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>100MB 사용할 경우 100MB x 1,000 = 100GB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
- - 메일 큐(1인당 100MB) 및 로그 저장용(1인당 300MB) x 사용자수
-   예) (0.1 + 0.3) x 1,000 = 400GB </t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> - 사용자당 대용량 첨부 파일저장용량 x 사용자수
-   예) 보관기간 14일 동안 사용자당 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>100MB 사용할 경우 100MB x 3,000 = 300GB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
- - 로그 저장용(1인당 200MB) x 사용자수
-   예) 0.2 x 3,000 = 600GB</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> - 사용자당 메일박스용량 x 1.2 x 사용자수
-   예) 사용자당 1GB일 경우 1GB x 1.2 x 3,000 = 3.6TB
- - 메일 큐(1인당 100MB) 및 로그 저장용(1인당 100MB) x 사용자수
-   예) (0.1 + 0.1) x 3,000 = 600GB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> - 사용자당 대용량 첨부 파일저장용량 x 사용자수
-   예) 보관기간 14일 동안 사용자당</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 100MB 사용할 경우 100MB x 5,000 = 500GB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
- - 로그 저장용(1인당 200MB) x 사용자수
-   예) 0.2 x 5,000 = 1TB</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> - 사용자당 메일박스용량 x 1.2 x 사용자수
-   예) 사용자당 1GB일 경우 1GB x 1.2 x 5,000 = 6TB
- - 메일 큐(1인당 100MB) 및 로그 저장용(1인당 100MB) x 사용자수 / 서버대수
-   예) (0.1 + 0.1) x 5,000 / 2 = 500GB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> - 사용자당 메일박스용량 x 1.2 x 사용자수
-   예) 사용자당 1GB일 경우 1GB x 1.2 x 10,000 = 12TB
- - 메일 큐(1인당 100MB) 및 로그 저장용(1인당 100MB) x 사용자수 / 서버대수
-   예) (0.1 + 0.1) x 10,000 / 2 = 1TB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> - 사용자당 대용량 첨부 파일저장용량 x 사용자수 / 서버대수
-   예) 보관기간 14일 동안 사용자당</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 100MB 사용할 경우 100MB x 10,000 / 2 = 500GB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
- - 로그 저장용(1인당 200MB) x 사용자수 / 서버대수
-   예) 0.2 x 10,000 / 2 = 1TB</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">시스템 도입 후 사용기간 </t>
   </si>
   <si>
@@ -435,14 +241,97 @@
 3(이중화)</t>
   </si>
   <si>
+    <t>게시,공지 첨부파일 등
+(1인당 1년 사용량)</t>
+  </si>
+  <si>
+    <t>그룹웨어 용량 / Mbytes</t>
+  </si>
+  <si>
+    <t>메일 용량 / Mbytes</t>
+  </si>
+  <si>
+    <t>메일 용량</t>
+  </si>
+  <si>
+    <t>대용량 첨부파일 (1인당 사용량)</t>
+  </si>
+  <si>
+    <t>대용량 첨부파일 14일간 보존 기준</t>
+  </si>
+  <si>
+    <t>그룹웨어 용량 (Tbytes)</t>
+  </si>
+  <si>
+    <t>메일 용량 (Tbytes)</t>
+  </si>
+  <si>
+    <t>로컬 시스템 용량 
+(Tbytes)</t>
+  </si>
+  <si>
+    <t>Disk 사용률 90%이하 유지 권장</t>
+  </si>
+  <si>
+    <t>메일 큐(1인당 100MB)및 LOG 사용량(1인당 300MB) (이중화시 서버간 공유되지 않음)</t>
+  </si>
+  <si>
+    <t>그룹웨어 용량</t>
+  </si>
+  <si>
+    <t>로컬 리스템 용량</t>
+  </si>
+  <si>
+    <t>이중화시 서버마다 다른 Data가 저장되는 용량</t>
+  </si>
+  <si>
+    <t>이중화시 서버간 동일 Data가 저장되는 DB Data 용량 
+(MariaDB의 경우엔 복제 방식이므로 서버당 용량이 필요하며  Oracle의 경우엔 Shared Disk 방식이므로 단일 용량만 필요)</t>
+  </si>
+  <si>
+    <t>이중화시 서버간 동일 Data가 저장되는 File Data 용량
+(GlusterFS의 경우엔 복제 방식이므로 서버당 용량이 필요하며 NAS 혹은 네트워크 파일 시스템을 사용할 경우엔 단일 용량만 필요)</t>
+  </si>
+  <si>
+    <t>DB 용량 (Tbytes)</t>
+  </si>
+  <si>
+    <t>DB 용량</t>
+  </si>
+  <si>
+    <t>그룹웨어 용량 + 
+메일 용량</t>
+  </si>
+  <si>
+    <t>MariaDB</t>
+  </si>
+  <si>
+    <t>Tomcat, GlusterFS(이중화 시), garbd(이중화 시)
+JMocha Mail Server</t>
+  </si>
+  <si>
+    <t>Tomcat, GlusterFS(이중화 시)
+JMocha Mail Server, MariaDB</t>
+  </si>
+  <si>
+    <t>1 x 6core
+2.4GHz</t>
+  </si>
+  <si>
+    <t>1 x 10core
+2.4GHz</t>
+  </si>
+  <si>
+    <t>32GB</t>
+  </si>
+  <si>
+    <t>48GB</t>
+  </si>
+  <si>
+    <t>16GB</t>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>2</t>
     </r>
     <r>
@@ -460,7 +349,7 @@
     <r>
       <rPr>
         <sz val="8"/>
-        <color rgb="FFFF0000"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -480,69 +369,28 @@
     </r>
   </si>
   <si>
-    <t>게시,공지 첨부파일 등
-(1인당 1년 사용량)</t>
-  </si>
-  <si>
-    <t>그룹웨어 용량 / Mbytes</t>
-  </si>
-  <si>
-    <t>메일 용량 / Mbytes</t>
-  </si>
-  <si>
-    <t>메일 용량</t>
-  </si>
-  <si>
-    <t>메일 사용(용량) 비율</t>
-  </si>
-  <si>
-    <t>메일 사용용량 비율</t>
-  </si>
-  <si>
-    <t>대용량 첨부파일 (1인당 사용량)</t>
-  </si>
-  <si>
-    <t>대용량 첨부파일 14일간 보존 기준</t>
-  </si>
-  <si>
-    <t>그룹웨어 용량 (Tbytes)</t>
-  </si>
-  <si>
-    <t>메일 용량 (Tbytes)</t>
-  </si>
-  <si>
-    <t>로컬 시스템 용량 
-(Tbytes)</t>
-  </si>
-  <si>
-    <t>Disk 사용률 90%이하 유지 권장</t>
-  </si>
-  <si>
-    <t>메일 큐(1인당 100MB)및 LOG 사용량(1인당 300MB) (이중화시 서버간 공유되지 않음)</t>
-  </si>
-  <si>
-    <t>그룹웨어 용량</t>
-  </si>
-  <si>
-    <t>로컬 리스템 용량</t>
-  </si>
-  <si>
-    <t>그룹웨어 용량 + 
-대용량 첨부파일</t>
-  </si>
-  <si>
-    <t>메일용량</t>
-  </si>
-  <si>
-    <t>이중화시 서버마다 다른 Data가 저장되는 용량</t>
-  </si>
-  <si>
-    <t>이중화시 서버간 동일 Data가 저장되는 DB Data 용량 
-(MariaDB의 경우엔 복제 방식이므로 서버당 용량이 필요하며  Oracle의 경우엔 Shared Disk 방식이므로 단일 용량만 필요)</t>
-  </si>
-  <si>
-    <t>이중화시 서버간 동일 Data가 저장되는 File Data 용량
-(GlusterFS의 경우엔 복제 방식이므로 서버당 용량이 필요하며 NAS 혹은 네트워크 파일 시스템을 사용할 경우엔 단일 용량만 필요)</t>
+    <t>Tomcat, GlusterFS(이중화 시)
+JMocha Mail Server</t>
+  </si>
+  <si>
+    <t>1 x 12core
+2.4GHz</t>
+  </si>
+  <si>
+    <t>1 x 20core
+2.4GHz</t>
+  </si>
+  <si>
+    <t>96GB</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 100GB</t>
+  </si>
+  <si>
+    <t>아래 계산표 참조</t>
+  </si>
+  <si>
+    <t>• garbd는 MariaDB Cluster의 노드수를 3개로 만들기 위해 사용하는 가상노드임</t>
   </si>
 </sst>
 </file>
@@ -558,7 +406,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.00\ &quot;%&quot;"/>
     <numFmt numFmtId="169" formatCode="#,##0.0000\ &quot;TB&quot;"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -631,15 +479,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -671,13 +510,6 @@
       <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -918,11 +750,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -956,58 +788,139 @@
     <xf numFmtId="41" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1021,96 +934,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="11" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="11" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1406,56 +1229,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="A1" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="31"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
     </row>
     <row r="3" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A3" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
+      <c r="A3" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A5" s="33" t="s">
-        <v>13</v>
+      <c r="A5" s="55" t="s">
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>1</v>
@@ -1464,64 +1287,64 @@
         <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="74.25" customHeight="1" thickBot="1">
-      <c r="A6" s="34"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="8" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="7" spans="1:7" ht="46.5" customHeight="1">
-      <c r="A7" s="35"/>
-      <c r="B7" s="19" t="s">
-        <v>51</v>
+      <c r="A7" s="52"/>
+      <c r="B7" s="18" t="s">
+        <v>43</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="9" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A9" s="33" t="s">
-        <v>14</v>
+      <c r="A9" s="55" t="s">
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>1</v>
@@ -1530,62 +1353,62 @@
         <v>2</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A10" s="34"/>
-      <c r="B10" s="20" t="s">
-        <v>52</v>
+      <c r="A10" s="51"/>
+      <c r="B10" s="18" t="s">
+        <v>68</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>28</v>
+        <v>81</v>
+      </c>
+      <c r="G10" s="53" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A11" s="35"/>
+      <c r="A11" s="52"/>
       <c r="B11" s="3" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="37"/>
+        <v>81</v>
+      </c>
+      <c r="G11" s="54"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="13" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A13" s="33" t="s">
-        <v>15</v>
+      <c r="A13" s="55" t="s">
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>1</v>
@@ -1594,62 +1417,62 @@
         <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A14" s="34"/>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="23" t="s">
+      <c r="A14" s="51"/>
+      <c r="B14" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="53" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="56.25" customHeight="1">
+      <c r="A15" s="52"/>
+      <c r="B15" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="36" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A15" s="35"/>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="C15" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" s="37"/>
+        <v>81</v>
+      </c>
+      <c r="G15" s="54"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="17" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A17" s="38" t="s">
-        <v>24</v>
+      <c r="A17" s="55" t="s">
+        <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>1</v>
@@ -1658,183 +1481,183 @@
         <v>2</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A18" s="34"/>
-      <c r="B18" s="3" t="s">
-        <v>9</v>
+      <c r="A18" s="51"/>
+      <c r="B18" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>79</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G18" s="36" t="s">
-        <v>30</v>
+        <v>81</v>
+      </c>
+      <c r="G18" s="53" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A19" s="35"/>
+      <c r="A19" s="52"/>
       <c r="B19" s="3" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>53</v>
+        <v>6</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>72</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19" s="37"/>
+        <v>81</v>
+      </c>
+      <c r="G19" s="54"/>
     </row>
     <row r="21" spans="1:7">
       <c r="B21" s="11" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="40"/>
+        <v>26</v>
+      </c>
+      <c r="F21" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="50"/>
     </row>
     <row r="22" spans="1:7">
       <c r="B22" s="12">
         <v>1</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D22" s="13">
         <v>1000</v>
       </c>
       <c r="E22" s="13"/>
-      <c r="F22" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="42"/>
+      <c r="F22" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="30"/>
     </row>
     <row r="23" spans="1:7" ht="25.5">
       <c r="B23" s="12">
         <v>2</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15"/>
-      <c r="F23" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" s="42"/>
+      <c r="F23" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="30"/>
     </row>
     <row r="24" spans="1:7" ht="25.5">
       <c r="B24" s="12">
         <v>3</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D24" s="14">
         <v>22</v>
       </c>
       <c r="E24" s="15"/>
-      <c r="F24" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="G24" s="42"/>
+      <c r="F24" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="30"/>
     </row>
     <row r="25" spans="1:7">
       <c r="B25" s="12">
         <v>4</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D25" s="14">
         <v>12</v>
       </c>
       <c r="E25" s="15"/>
-      <c r="F25" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="G25" s="42"/>
+      <c r="F25" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="30"/>
     </row>
     <row r="26" spans="1:7" ht="25.5">
       <c r="B26" s="12">
         <v>5</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D26" s="14">
         <v>5</v>
       </c>
       <c r="E26" s="15"/>
-      <c r="F26" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="G26" s="42"/>
+      <c r="F26" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" s="30"/>
     </row>
     <row r="27" spans="1:7" ht="25.5">
       <c r="B27" s="12">
         <v>6</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D27" s="14">
         <v>0.3</v>
       </c>
       <c r="E27" s="16"/>
-      <c r="F27" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="G27" s="42"/>
+      <c r="F27" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="G27" s="30"/>
     </row>
     <row r="28" spans="1:7" ht="51">
       <c r="B28" s="12">
         <v>7</v>
       </c>
-      <c r="C28" s="27" t="s">
-        <v>68</v>
+      <c r="C28" s="25" t="s">
+        <v>48</v>
       </c>
       <c r="D28" s="14">
         <v>100</v>
       </c>
       <c r="E28" s="16"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="26"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="24"/>
     </row>
     <row r="29" spans="1:7">
       <c r="B29" s="43" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C29" s="44"/>
       <c r="D29" s="45">
@@ -1850,206 +1673,208 @@
         <v>1</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D30" s="14">
         <v>1000</v>
       </c>
       <c r="E30" s="15"/>
-      <c r="F30" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="G30" s="42"/>
-    </row>
-    <row r="31" spans="1:7" ht="38.25">
+      <c r="F30" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="G30" s="30"/>
+    </row>
+    <row r="31" spans="1:7" ht="51">
       <c r="B31" s="12">
         <v>2</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" s="17">
+      <c r="C31" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="14">
+        <v>100</v>
+      </c>
+      <c r="E31" s="26"/>
+      <c r="F31" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" s="24"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="B32" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="44"/>
+      <c r="D32" s="45">
+        <f>D22*D30 + D22*D31</f>
+        <v>1100000</v>
+      </c>
+      <c r="E32" s="46"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="48"/>
+    </row>
+    <row r="33" spans="2:7" ht="38.25">
+      <c r="B33" s="12">
         <v>1</v>
       </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="G31" s="42"/>
-    </row>
-    <row r="32" spans="1:7" ht="51">
-      <c r="B32" s="12">
-        <v>3</v>
-      </c>
-      <c r="C32" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" s="14">
-        <v>100</v>
-      </c>
-      <c r="E32" s="28"/>
-      <c r="F32" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="G32" s="26"/>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="43" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" s="44"/>
-      <c r="D33" s="45">
-        <f>D22*D30*1.2*D31 + D22*D32</f>
-        <v>1300000</v>
-      </c>
-      <c r="E33" s="46"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="48"/>
-    </row>
-    <row r="34" spans="2:7" ht="38.25">
-      <c r="B34" s="12">
-        <v>1</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" s="55">
+      <c r="C33" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="37">
         <f>0.0001*D22 + 0.0003*D22</f>
         <v>0.4</v>
       </c>
-      <c r="E34" s="56"/>
-      <c r="F34" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="G34" s="42"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33" s="30"/>
+    </row>
+    <row r="34" spans="2:7" ht="25.5">
+      <c r="B34" s="12">
+        <v>2</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="39">
+        <f>D29/1000000</f>
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="E34" s="40"/>
+      <c r="F34" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34" s="30"/>
     </row>
     <row r="35" spans="2:7" ht="25.5">
       <c r="B35" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D35" s="57">
-        <f>D29/1000000</f>
-        <v>0.89600000000000002</v>
-      </c>
-      <c r="E35" s="58"/>
-      <c r="F35" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="G35" s="42"/>
+        <v>55</v>
+      </c>
+      <c r="D35" s="41">
+        <f>D32/1000000</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E35" s="42"/>
+      <c r="F35" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="G35" s="30"/>
     </row>
     <row r="36" spans="2:7" ht="25.5">
       <c r="B36" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D36" s="59">
-        <f>D33/1000000</f>
-        <v>1.3</v>
-      </c>
-      <c r="E36" s="60"/>
-      <c r="F36" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="G36" s="42"/>
+        <v>64</v>
+      </c>
+      <c r="D36" s="41">
+        <f>(D22*D30*0.2)/1000000</f>
+        <v>0.2</v>
+      </c>
+      <c r="E36" s="42"/>
+      <c r="F36" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="G36" s="30"/>
     </row>
     <row r="37" spans="2:7" ht="25.5">
       <c r="B37" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D37" s="24">
+        <v>40</v>
+      </c>
+      <c r="D37" s="22">
         <v>10</v>
       </c>
-      <c r="E37" s="18">
-        <f>SUM(D34:E36)/(1 - D37/100)</f>
+      <c r="E37" s="17">
+        <f>SUM(D33:E36)/(1 - D37/100)</f>
         <v>2.8844444444444446</v>
       </c>
-      <c r="F37" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="G37" s="42"/>
+      <c r="F37" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="G37" s="30"/>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="C38" s="50"/>
-      <c r="D38" s="51">
+      <c r="B38" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="32"/>
+      <c r="D38" s="33">
         <f>E37</f>
         <v>2.8844444444444446</v>
       </c>
-      <c r="E38" s="52"/>
-      <c r="F38" s="53"/>
-      <c r="G38" s="54"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="36"/>
     </row>
     <row r="40" spans="2:7" ht="30">
-      <c r="B40" s="62" t="s">
-        <v>85</v>
-      </c>
-      <c r="C40" s="61" t="s">
-        <v>82</v>
+      <c r="B40" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="2:7" ht="90">
-      <c r="B41" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" s="61" t="s">
-        <v>83</v>
+      <c r="B41" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" s="27" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="90">
-      <c r="B42" s="62" t="s">
-        <v>86</v>
-      </c>
-      <c r="C42" s="61" t="s">
-        <v>84</v>
+      <c r="B42" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="27" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="36">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="D38:E38"/>
     <mergeCell ref="F38:G38"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G10:G11"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/tech/ezEKP_시스템_사이징_사용자수별.xlsx
+++ b/docs/tech/ezEKP_시스템_사이징_사용자수별.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="82">
   <si>
     <t>Software</t>
   </si>
@@ -304,14 +304,6 @@
   </si>
   <si>
     <t>MariaDB</t>
-  </si>
-  <si>
-    <t>Tomcat, GlusterFS(이중화 시), garbd(이중화 시)
-JMocha Mail Server</t>
-  </si>
-  <si>
-    <t>Tomcat, GlusterFS(이중화 시)
-JMocha Mail Server, MariaDB</t>
   </si>
   <si>
     <t>1 x 6core
@@ -369,10 +361,6 @@
     </r>
   </si>
   <si>
-    <t>Tomcat, GlusterFS(이중화 시)
-JMocha Mail Server</t>
-  </si>
-  <si>
     <t>1 x 12core
 2.4GHz</t>
   </si>
@@ -391,6 +379,14 @@
   </si>
   <si>
     <t>• garbd는 MariaDB Cluster의 노드수를 3개로 만들기 위해 사용하는 가상노드임</t>
+  </si>
+  <si>
+    <t>Tomcat,
+JMocha Mail Server, MariaDB</t>
+  </si>
+  <si>
+    <t>Tomcat,
+JMocha Mail Server</t>
   </si>
 </sst>
 </file>
@@ -842,11 +838,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -883,57 +930,6 @@
     </xf>
     <xf numFmtId="167" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1229,49 +1225,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="58"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="33" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1294,9 +1290,9 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="74.25" customHeight="1" thickBot="1">
-      <c r="A6" s="51"/>
+      <c r="A6" s="34"/>
       <c r="B6" s="8" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>5</v>
@@ -1308,14 +1304,14 @@
         <v>14</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="46.5" customHeight="1">
-      <c r="A7" s="52"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="18" t="s">
         <v>43</v>
       </c>
@@ -1329,15 +1325,15 @@
         <v>16</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="9" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1360,28 +1356,28 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A10" s="51"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="18" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="F10" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G10" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" s="36" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A11" s="52"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="3" t="s">
         <v>67</v>
       </c>
@@ -1389,19 +1385,19 @@
         <v>5</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G11" s="54"/>
+        <v>78</v>
+      </c>
+      <c r="G11" s="37"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="13" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="33" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1424,28 +1420,28 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A14" s="51"/>
+      <c r="A14" s="34"/>
       <c r="B14" s="8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D14" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="F14" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="36" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A15" s="52"/>
+      <c r="A15" s="35"/>
       <c r="B15" s="3" t="s">
         <v>67</v>
       </c>
@@ -1453,19 +1449,19 @@
         <v>6</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="54"/>
+        <v>78</v>
+      </c>
+      <c r="G15" s="37"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="17" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A17" s="55" t="s">
+      <c r="A17" s="33" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1488,28 +1484,28 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A18" s="51"/>
+      <c r="A18" s="34"/>
       <c r="B18" s="8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>47</v>
       </c>
       <c r="D18" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G18" s="53" t="s">
+      <c r="G18" s="36" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A19" s="52"/>
+      <c r="A19" s="35"/>
       <c r="B19" s="3" t="s">
         <v>67</v>
       </c>
@@ -1517,15 +1513,15 @@
         <v>6</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" s="54"/>
+        <v>78</v>
+      </c>
+      <c r="G19" s="37"/>
     </row>
     <row r="21" spans="1:7">
       <c r="B21" s="11" t="s">
@@ -1540,10 +1536,10 @@
       <c r="E21" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="49" t="s">
+      <c r="F21" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="G21" s="50"/>
+      <c r="G21" s="39"/>
     </row>
     <row r="22" spans="1:7">
       <c r="B22" s="12">
@@ -1556,10 +1552,10 @@
         <v>1000</v>
       </c>
       <c r="E22" s="13"/>
-      <c r="F22" s="29" t="s">
+      <c r="F22" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="30"/>
+      <c r="G22" s="41"/>
     </row>
     <row r="23" spans="1:7" ht="25.5">
       <c r="B23" s="12">
@@ -1572,10 +1568,10 @@
         <v>1</v>
       </c>
       <c r="E23" s="15"/>
-      <c r="F23" s="29" t="s">
+      <c r="F23" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="30"/>
+      <c r="G23" s="41"/>
     </row>
     <row r="24" spans="1:7" ht="25.5">
       <c r="B24" s="12">
@@ -1588,10 +1584,10 @@
         <v>22</v>
       </c>
       <c r="E24" s="15"/>
-      <c r="F24" s="29" t="s">
+      <c r="F24" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="30"/>
+      <c r="G24" s="41"/>
     </row>
     <row r="25" spans="1:7">
       <c r="B25" s="12">
@@ -1604,10 +1600,10 @@
         <v>12</v>
       </c>
       <c r="E25" s="15"/>
-      <c r="F25" s="29" t="s">
+      <c r="F25" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="G25" s="30"/>
+      <c r="G25" s="41"/>
     </row>
     <row r="26" spans="1:7" ht="25.5">
       <c r="B26" s="12">
@@ -1620,10 +1616,10 @@
         <v>5</v>
       </c>
       <c r="E26" s="15"/>
-      <c r="F26" s="29" t="s">
+      <c r="F26" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="G26" s="30"/>
+      <c r="G26" s="41"/>
     </row>
     <row r="27" spans="1:7" ht="25.5">
       <c r="B27" s="12">
@@ -1636,10 +1632,10 @@
         <v>0.3</v>
       </c>
       <c r="E27" s="16"/>
-      <c r="F27" s="29" t="s">
+      <c r="F27" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="G27" s="30"/>
+      <c r="G27" s="41"/>
     </row>
     <row r="28" spans="1:7" ht="51">
       <c r="B28" s="12">
@@ -1656,17 +1652,17 @@
       <c r="G28" s="24"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="B29" s="43" t="s">
+      <c r="B29" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="44"/>
-      <c r="D29" s="45">
+      <c r="C29" s="43"/>
+      <c r="D29" s="44">
         <f>D22*D23*D24*D25*D26*D27 + D22*D26*D28</f>
         <v>896000</v>
       </c>
-      <c r="E29" s="46"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="48"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="47"/>
     </row>
     <row r="30" spans="1:7" ht="25.5">
       <c r="B30" s="12">
@@ -1679,10 +1675,10 @@
         <v>1000</v>
       </c>
       <c r="E30" s="15"/>
-      <c r="F30" s="29" t="s">
+      <c r="F30" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="30"/>
+      <c r="G30" s="41"/>
     </row>
     <row r="31" spans="1:7" ht="51">
       <c r="B31" s="12">
@@ -1701,17 +1697,17 @@
       <c r="G31" s="24"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="B32" s="43" t="s">
+      <c r="B32" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="44"/>
-      <c r="D32" s="45">
+      <c r="C32" s="43"/>
+      <c r="D32" s="44">
         <f>D22*D30 + D22*D31</f>
         <v>1100000</v>
       </c>
-      <c r="E32" s="46"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="48"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="47"/>
     </row>
     <row r="33" spans="2:7" ht="38.25">
       <c r="B33" s="12">
@@ -1720,15 +1716,15 @@
       <c r="C33" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="37">
+      <c r="D33" s="54">
         <f>0.0001*D22 + 0.0003*D22</f>
         <v>0.4</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="29" t="s">
+      <c r="E33" s="55"/>
+      <c r="F33" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="30"/>
+      <c r="G33" s="41"/>
     </row>
     <row r="34" spans="2:7" ht="25.5">
       <c r="B34" s="12">
@@ -1737,15 +1733,15 @@
       <c r="C34" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="39">
+      <c r="D34" s="56">
         <f>D29/1000000</f>
         <v>0.89600000000000002</v>
       </c>
-      <c r="E34" s="40"/>
-      <c r="F34" s="29" t="s">
+      <c r="E34" s="57"/>
+      <c r="F34" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="30"/>
+      <c r="G34" s="41"/>
     </row>
     <row r="35" spans="2:7" ht="25.5">
       <c r="B35" s="12">
@@ -1754,15 +1750,15 @@
       <c r="C35" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="41">
+      <c r="D35" s="58">
         <f>D32/1000000</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="E35" s="42"/>
-      <c r="F35" s="29" t="s">
+      <c r="E35" s="59"/>
+      <c r="F35" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="G35" s="30"/>
+      <c r="G35" s="41"/>
     </row>
     <row r="36" spans="2:7" ht="25.5">
       <c r="B36" s="12">
@@ -1771,15 +1767,15 @@
       <c r="C36" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="41">
+      <c r="D36" s="58">
         <f>(D22*D30*0.2)/1000000</f>
         <v>0.2</v>
       </c>
-      <c r="E36" s="42"/>
-      <c r="F36" s="29" t="s">
+      <c r="E36" s="59"/>
+      <c r="F36" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="G36" s="30"/>
+      <c r="G36" s="41"/>
     </row>
     <row r="37" spans="2:7" ht="25.5">
       <c r="B37" s="12">
@@ -1795,23 +1791,23 @@
         <f>SUM(D33:E36)/(1 - D37/100)</f>
         <v>2.8844444444444446</v>
       </c>
-      <c r="F37" s="29" t="s">
+      <c r="F37" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="G37" s="30"/>
+      <c r="G37" s="41"/>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="31" t="s">
+      <c r="B38" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="32"/>
-      <c r="D38" s="33">
+      <c r="C38" s="49"/>
+      <c r="D38" s="50">
         <f>E37</f>
         <v>2.8844444444444446</v>
       </c>
-      <c r="E38" s="34"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="36"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="53"/>
     </row>
     <row r="40" spans="2:7" ht="30">
       <c r="B40" s="28" t="s">
@@ -1839,31 +1835,6 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F37:G37"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="D38:E38"/>
     <mergeCell ref="F38:G38"/>
@@ -1875,6 +1846,31 @@
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="G10:G11"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/tech/ezEKP_시스템_사이징_사용자수별.xlsx
+++ b/docs/tech/ezEKP_시스템_사이징_사용자수별.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="78">
   <si>
     <t>Software</t>
   </si>
@@ -306,21 +306,7 @@
     <t>MariaDB</t>
   </si>
   <si>
-    <t>1 x 6core
-2.4GHz</t>
-  </si>
-  <si>
-    <t>1 x 10core
-2.4GHz</t>
-  </si>
-  <si>
     <t>32GB</t>
-  </si>
-  <si>
-    <t>48GB</t>
-  </si>
-  <si>
-    <t>16GB</t>
   </si>
   <si>
     <r>
@@ -361,17 +347,6 @@
     </r>
   </si>
   <si>
-    <t>1 x 12core
-2.4GHz</t>
-  </si>
-  <si>
-    <t>1 x 20core
-2.4GHz</t>
-  </si>
-  <si>
-    <t>96GB</t>
-  </si>
-  <si>
     <t xml:space="preserve"> - 100GB</t>
   </si>
   <si>
@@ -387,6 +362,17 @@
   <si>
     <t>Tomcat,
 JMocha Mail Server</t>
+  </si>
+  <si>
+    <t>1 x 8core
+2.4GHz</t>
+  </si>
+  <si>
+    <t>1 x 16core
+2.4GHz</t>
+  </si>
+  <si>
+    <t>64GB</t>
   </si>
 </sst>
 </file>
@@ -838,6 +824,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -849,87 +916,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1225,49 +1211,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="31"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
     </row>
     <row r="3" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="51" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1290,9 +1276,9 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="74.25" customHeight="1" thickBot="1">
-      <c r="A6" s="34"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="8" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>5</v>
@@ -1304,14 +1290,14 @@
         <v>14</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="46.5" customHeight="1">
-      <c r="A7" s="35"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="18" t="s">
         <v>43</v>
       </c>
@@ -1325,15 +1311,15 @@
         <v>16</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="9" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="51" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1356,28 +1342,28 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A10" s="34"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="18" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="54" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A11" s="35"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="3" t="s">
         <v>67</v>
       </c>
@@ -1385,19 +1371,19 @@
         <v>5</v>
       </c>
       <c r="D11" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>72</v>
-      </c>
       <c r="F11" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" s="37"/>
+        <v>71</v>
+      </c>
+      <c r="G11" s="55"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="13" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="51" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1420,28 +1406,28 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A14" s="34"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="8" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" s="36" t="s">
+      <c r="G14" s="54" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A15" s="35"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="3" t="s">
         <v>67</v>
       </c>
@@ -1449,19 +1435,19 @@
         <v>6</v>
       </c>
       <c r="D15" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>72</v>
-      </c>
       <c r="F15" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="37"/>
+        <v>71</v>
+      </c>
+      <c r="G15" s="55"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="17" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="51" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1484,28 +1470,28 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A18" s="34"/>
+      <c r="A18" s="52"/>
       <c r="B18" s="8" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>47</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="54" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A19" s="35"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="3" t="s">
         <v>67</v>
       </c>
@@ -1513,15 +1499,15 @@
         <v>6</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="37"/>
+        <v>71</v>
+      </c>
+      <c r="G19" s="55"/>
     </row>
     <row r="21" spans="1:7">
       <c r="B21" s="11" t="s">
@@ -1536,10 +1522,10 @@
       <c r="E21" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="38" t="s">
+      <c r="F21" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="G21" s="39"/>
+      <c r="G21" s="50"/>
     </row>
     <row r="22" spans="1:7">
       <c r="B22" s="12">
@@ -1552,10 +1538,10 @@
         <v>1000</v>
       </c>
       <c r="E22" s="13"/>
-      <c r="F22" s="40" t="s">
+      <c r="F22" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="41"/>
+      <c r="G22" s="38"/>
     </row>
     <row r="23" spans="1:7" ht="25.5">
       <c r="B23" s="12">
@@ -1568,10 +1554,10 @@
         <v>1</v>
       </c>
       <c r="E23" s="15"/>
-      <c r="F23" s="40" t="s">
+      <c r="F23" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="41"/>
+      <c r="G23" s="38"/>
     </row>
     <row r="24" spans="1:7" ht="25.5">
       <c r="B24" s="12">
@@ -1584,10 +1570,10 @@
         <v>22</v>
       </c>
       <c r="E24" s="15"/>
-      <c r="F24" s="40" t="s">
+      <c r="F24" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="41"/>
+      <c r="G24" s="38"/>
     </row>
     <row r="25" spans="1:7">
       <c r="B25" s="12">
@@ -1600,10 +1586,10 @@
         <v>12</v>
       </c>
       <c r="E25" s="15"/>
-      <c r="F25" s="40" t="s">
+      <c r="F25" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="G25" s="41"/>
+      <c r="G25" s="38"/>
     </row>
     <row r="26" spans="1:7" ht="25.5">
       <c r="B26" s="12">
@@ -1616,10 +1602,10 @@
         <v>5</v>
       </c>
       <c r="E26" s="15"/>
-      <c r="F26" s="40" t="s">
+      <c r="F26" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="G26" s="41"/>
+      <c r="G26" s="38"/>
     </row>
     <row r="27" spans="1:7" ht="25.5">
       <c r="B27" s="12">
@@ -1632,10 +1618,10 @@
         <v>0.3</v>
       </c>
       <c r="E27" s="16"/>
-      <c r="F27" s="40" t="s">
+      <c r="F27" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="G27" s="41"/>
+      <c r="G27" s="38"/>
     </row>
     <row r="28" spans="1:7" ht="51">
       <c r="B28" s="12">
@@ -1652,17 +1638,17 @@
       <c r="G28" s="24"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="B29" s="42" t="s">
+      <c r="B29" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="43"/>
-      <c r="D29" s="44">
+      <c r="C29" s="44"/>
+      <c r="D29" s="45">
         <f>D22*D23*D24*D25*D26*D27 + D22*D26*D28</f>
         <v>896000</v>
       </c>
-      <c r="E29" s="45"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="47"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="48"/>
     </row>
     <row r="30" spans="1:7" ht="25.5">
       <c r="B30" s="12">
@@ -1675,10 +1661,10 @@
         <v>1000</v>
       </c>
       <c r="E30" s="15"/>
-      <c r="F30" s="40" t="s">
+      <c r="F30" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="41"/>
+      <c r="G30" s="38"/>
     </row>
     <row r="31" spans="1:7" ht="51">
       <c r="B31" s="12">
@@ -1697,17 +1683,17 @@
       <c r="G31" s="24"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="B32" s="42" t="s">
+      <c r="B32" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="43"/>
-      <c r="D32" s="44">
+      <c r="C32" s="44"/>
+      <c r="D32" s="45">
         <f>D22*D30 + D22*D31</f>
         <v>1100000</v>
       </c>
-      <c r="E32" s="45"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="47"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="48"/>
     </row>
     <row r="33" spans="2:7" ht="38.25">
       <c r="B33" s="12">
@@ -1716,15 +1702,15 @@
       <c r="C33" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="54">
+      <c r="D33" s="35">
         <f>0.0001*D22 + 0.0003*D22</f>
         <v>0.4</v>
       </c>
-      <c r="E33" s="55"/>
-      <c r="F33" s="40" t="s">
+      <c r="E33" s="36"/>
+      <c r="F33" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="41"/>
+      <c r="G33" s="38"/>
     </row>
     <row r="34" spans="2:7" ht="25.5">
       <c r="B34" s="12">
@@ -1733,15 +1719,15 @@
       <c r="C34" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="56">
+      <c r="D34" s="39">
         <f>D29/1000000</f>
         <v>0.89600000000000002</v>
       </c>
-      <c r="E34" s="57"/>
-      <c r="F34" s="40" t="s">
+      <c r="E34" s="40"/>
+      <c r="F34" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="41"/>
+      <c r="G34" s="38"/>
     </row>
     <row r="35" spans="2:7" ht="25.5">
       <c r="B35" s="12">
@@ -1750,15 +1736,15 @@
       <c r="C35" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="58">
+      <c r="D35" s="41">
         <f>D32/1000000</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="E35" s="59"/>
-      <c r="F35" s="40" t="s">
+      <c r="E35" s="42"/>
+      <c r="F35" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="G35" s="41"/>
+      <c r="G35" s="38"/>
     </row>
     <row r="36" spans="2:7" ht="25.5">
       <c r="B36" s="12">
@@ -1767,15 +1753,15 @@
       <c r="C36" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="58">
+      <c r="D36" s="41">
         <f>(D22*D30*0.2)/1000000</f>
         <v>0.2</v>
       </c>
-      <c r="E36" s="59"/>
-      <c r="F36" s="40" t="s">
+      <c r="E36" s="42"/>
+      <c r="F36" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="G36" s="41"/>
+      <c r="G36" s="38"/>
     </row>
     <row r="37" spans="2:7" ht="25.5">
       <c r="B37" s="12">
@@ -1791,23 +1777,23 @@
         <f>SUM(D33:E36)/(1 - D37/100)</f>
         <v>2.8844444444444446</v>
       </c>
-      <c r="F37" s="40" t="s">
+      <c r="F37" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="G37" s="41"/>
+      <c r="G37" s="38"/>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="48" t="s">
+      <c r="B38" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="49"/>
-      <c r="D38" s="50">
+      <c r="C38" s="30"/>
+      <c r="D38" s="31">
         <f>E37</f>
         <v>2.8844444444444446</v>
       </c>
-      <c r="E38" s="51"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="53"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="34"/>
     </row>
     <row r="40" spans="2:7" ht="30">
       <c r="B40" s="28" t="s">
@@ -1835,6 +1821,31 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F37:G37"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="D38:E38"/>
     <mergeCell ref="F38:G38"/>
@@ -1846,31 +1857,6 @@
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G10:G11"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
